--- a/Colocalization/data.xlsx
+++ b/Colocalization/data.xlsx
@@ -1037,10 +1037,10 @@
     <t>41828496</t>
   </si>
   <si>
-    <t>41829779</t>
+    <t>41829296</t>
   </si>
   <si>
-    <t>41829296</t>
+    <t>41829779</t>
   </si>
   <si>
     <t>41835215</t>
@@ -6942,13 +6942,13 @@
         <v>0.03402</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0260167</v>
+        <v>-0.0244466</v>
       </c>
       <c r="I48" t="n">
         <v>0.2608</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07303700000000002</v>
+        <v>0.07582900000000004</v>
       </c>
       <c r="K48" t="s">
         <v>251</v>
@@ -6966,16 +6966,16 @@
         <v>55</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.00355141</v>
+        <v>0.00349056</v>
       </c>
       <c r="R48" t="n">
         <v>426824.0</v>
       </c>
       <c r="S48" t="n">
-        <v>6.90001E-10</v>
+        <v>2.0E-9</v>
       </c>
       <c r="T48" t="s">
         <v>18</v>
@@ -6999,7 +6999,7 @@
         <v>189</v>
       </c>
       <c r="AA48" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AB48" t="s">
         <v>247</v>
@@ -7008,10 +7008,10 @@
         <v>250</v>
       </c>
       <c r="AD48" t="s">
+        <v>249</v>
+      </c>
+      <c r="AE48" t="s">
         <v>247</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>250</v>
       </c>
       <c r="AF48" t="n">
         <v>0.094391</v>
@@ -11944,13 +11944,13 @@
         <v>0.028178</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.0181372</v>
+        <v>-0.0180004</v>
       </c>
       <c r="I89" t="n">
         <v>0.669</v>
       </c>
       <c r="J89" t="n">
-        <v>0.5738099999999999</v>
+        <v>0.5749960000000001</v>
       </c>
       <c r="K89" t="s">
         <v>251</v>
@@ -11971,13 +11971,13 @@
         <v>339</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.00187369</v>
+        <v>0.00187438</v>
       </c>
       <c r="R89" t="n">
         <v>426824.0</v>
       </c>
       <c r="S89" t="n">
-        <v>1.0E-18</v>
+        <v>1.20005E-18</v>
       </c>
       <c r="T89" t="s">
         <v>18</v>
@@ -12001,7 +12001,7 @@
         <v>230</v>
       </c>
       <c r="AA89" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AB89" t="s">
         <v>250</v>
@@ -12010,10 +12010,10 @@
         <v>249</v>
       </c>
       <c r="AD89" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AE89" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF89" t="n">
         <v>0.012771</v>
@@ -12090,7 +12090,7 @@
         <v>55</v>
       </c>
       <c r="P90" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q90" t="n">
         <v>0.00187438</v>
@@ -12212,7 +12212,7 @@
         <v>55</v>
       </c>
       <c r="P91" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q91" t="n">
         <v>0.00187369</v>
@@ -28958,13 +28958,13 @@
         <v>0.03402</v>
       </c>
       <c r="H46" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="I46" t="n">
         <v>0.2608</v>
       </c>
       <c r="J46" t="n">
-        <v>0.09540000000000004</v>
+        <v>0.08740000000000003</v>
       </c>
       <c r="K46" t="s">
         <v>251</v>
@@ -28982,16 +28982,16 @@
         <v>55</v>
       </c>
       <c r="P46" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0101</v>
+        <v>0.0105</v>
       </c>
       <c r="R46" t="n">
         <v>296525.0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.551899</v>
+        <v>0.772999</v>
       </c>
       <c r="T46" t="s">
         <v>18</v>
@@ -29015,7 +29015,7 @@
         <v>189</v>
       </c>
       <c r="AA46" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AB46" t="s">
         <v>247</v>
@@ -29024,10 +29024,10 @@
         <v>250</v>
       </c>
       <c r="AD46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AE46" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AF46" t="n">
         <v>0.094391</v>
@@ -33838,13 +33838,13 @@
         <v>0.028178</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0126</v>
+        <v>0.0125</v>
       </c>
       <c r="I86" t="n">
         <v>0.669</v>
       </c>
       <c r="J86" t="n">
-        <v>0.5723</v>
+        <v>0.5714</v>
       </c>
       <c r="K86" t="s">
         <v>251</v>
@@ -33871,7 +33871,7 @@
         <v>296525.0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0272998</v>
+        <v>0.02751</v>
       </c>
       <c r="T86" t="s">
         <v>18</v>
@@ -33895,7 +33895,7 @@
         <v>230</v>
       </c>
       <c r="AA86" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AB86" t="s">
         <v>250</v>
@@ -33904,10 +33904,10 @@
         <v>249</v>
       </c>
       <c r="AD86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE86" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF86" t="n">
         <v>0.012771</v>
@@ -33984,7 +33984,7 @@
         <v>55</v>
       </c>
       <c r="P87" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q87" t="n">
         <v>0.0057</v>
@@ -34106,7 +34106,7 @@
         <v>55</v>
       </c>
       <c r="P88" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q88" t="n">
         <v>0.0057</v>
@@ -46192,7 +46192,7 @@
         <v>55</v>
       </c>
       <c r="P85" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q85" t="n">
         <v>0.007509</v>
@@ -46314,7 +46314,7 @@
         <v>55</v>
       </c>
       <c r="P86" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q86" t="n">
         <v>0.007515</v>
@@ -67567,7 +67567,7 @@
         <v>55</v>
       </c>
       <c r="P90" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q90" t="n">
         <v>9.10266E-4</v>
@@ -67689,7 +67689,7 @@
         <v>55</v>
       </c>
       <c r="P91" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q91" t="n">
         <v>9.10619E-4</v>
@@ -67811,7 +67811,7 @@
         <v>55</v>
       </c>
       <c r="P92" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q92" t="n">
         <v>9.10266E-4</v>
@@ -78067,7 +78067,7 @@
         <v>55</v>
       </c>
       <c r="P70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q70" t="n">
         <v>0.0084</v>
@@ -78189,7 +78189,7 @@
         <v>55</v>
       </c>
       <c r="P71" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q71" t="n">
         <v>0.0084</v>
@@ -78311,7 +78311,7 @@
         <v>55</v>
       </c>
       <c r="P72" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q72" t="n">
         <v>0.0082</v>

--- a/Colocalization/data.xlsx
+++ b/Colocalization/data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13111" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13111" uniqueCount="372">
   <si>
     <t>SNP</t>
   </si>
@@ -1130,16 +1130,10 @@
     <t xml:space="preserve">Non-cancer illness code, self-reported: hypertension ||  || </t>
   </si>
   <si>
-    <t>41858742</t>
-  </si>
-  <si>
     <t>Type 2 diabetes</t>
   </si>
   <si>
     <t xml:space="preserve">Type 2 diabetes ||  || </t>
-  </si>
-  <si>
-    <t>rs113555429</t>
   </si>
 </sst>
 </file>
@@ -62541,13 +62535,13 @@
         <v>0.03402</v>
       </c>
       <c r="H49" t="n">
-        <v>-4.70585E-4</v>
+        <v>-0.00103282</v>
       </c>
       <c r="I49" t="n">
         <v>0.2608</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07318599999999997</v>
+        <v>0.07655500000000004</v>
       </c>
       <c r="K49" t="s">
         <v>251</v>
@@ -62565,16 +62559,16 @@
         <v>55</v>
       </c>
       <c r="P49" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.00172462</v>
+        <v>0.00168897</v>
       </c>
       <c r="R49" t="n">
         <v>462933.0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.780001</v>
+        <v>0.54</v>
       </c>
       <c r="T49" t="s">
         <v>18</v>
@@ -62598,7 +62592,7 @@
         <v>189</v>
       </c>
       <c r="AA49" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AB49" t="s">
         <v>247</v>
@@ -62607,10 +62601,10 @@
         <v>250</v>
       </c>
       <c r="AD49" t="s">
+        <v>249</v>
+      </c>
+      <c r="AE49" t="s">
         <v>247</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>250</v>
       </c>
       <c r="AF49" t="n">
         <v>0.094391</v>
@@ -67543,13 +67537,13 @@
         <v>0.028178</v>
       </c>
       <c r="H90" t="n">
-        <v>-8.79383E-5</v>
+        <v>-2.3434E-4</v>
       </c>
       <c r="I90" t="n">
         <v>0.669</v>
       </c>
       <c r="J90" t="n">
-        <v>0.5747340000000001</v>
+        <v>0.575968</v>
       </c>
       <c r="K90" t="s">
         <v>251</v>
@@ -67567,16 +67561,16 @@
         <v>55</v>
       </c>
       <c r="P90" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q90" t="n">
-        <v>9.10266E-4</v>
+        <v>9.10619E-4</v>
       </c>
       <c r="R90" t="n">
         <v>462933.0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="T90" t="s">
         <v>18</v>
@@ -67600,7 +67594,7 @@
         <v>230</v>
       </c>
       <c r="AA90" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AB90" t="s">
         <v>250</v>
@@ -67609,10 +67603,10 @@
         <v>249</v>
       </c>
       <c r="AD90" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AE90" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF90" t="n">
         <v>0.012771</v>
@@ -69786,10 +69780,10 @@
         <v>18</v>
       </c>
       <c r="U2" t="s">
+        <v>370</v>
+      </c>
+      <c r="V2" t="s">
         <v>371</v>
-      </c>
-      <c r="V2" t="s">
-        <v>372</v>
       </c>
       <c r="W2" t="s">
         <v>252</v>
@@ -69908,10 +69902,10 @@
         <v>18</v>
       </c>
       <c r="U3" t="s">
+        <v>370</v>
+      </c>
+      <c r="V3" t="s">
         <v>371</v>
-      </c>
-      <c r="V3" t="s">
-        <v>372</v>
       </c>
       <c r="W3" t="s">
         <v>252</v>
@@ -70030,10 +70024,10 @@
         <v>18</v>
       </c>
       <c r="U4" t="s">
+        <v>370</v>
+      </c>
+      <c r="V4" t="s">
         <v>371</v>
-      </c>
-      <c r="V4" t="s">
-        <v>372</v>
       </c>
       <c r="W4" t="s">
         <v>252</v>
@@ -70152,10 +70146,10 @@
         <v>18</v>
       </c>
       <c r="U5" t="s">
+        <v>370</v>
+      </c>
+      <c r="V5" t="s">
         <v>371</v>
-      </c>
-      <c r="V5" t="s">
-        <v>372</v>
       </c>
       <c r="W5" t="s">
         <v>252</v>
@@ -70274,10 +70268,10 @@
         <v>18</v>
       </c>
       <c r="U6" t="s">
+        <v>370</v>
+      </c>
+      <c r="V6" t="s">
         <v>371</v>
-      </c>
-      <c r="V6" t="s">
-        <v>372</v>
       </c>
       <c r="W6" t="s">
         <v>252</v>
@@ -70396,10 +70390,10 @@
         <v>18</v>
       </c>
       <c r="U7" t="s">
+        <v>370</v>
+      </c>
+      <c r="V7" t="s">
         <v>371</v>
-      </c>
-      <c r="V7" t="s">
-        <v>372</v>
       </c>
       <c r="W7" t="s">
         <v>252</v>
@@ -70518,10 +70512,10 @@
         <v>18</v>
       </c>
       <c r="U8" t="s">
+        <v>370</v>
+      </c>
+      <c r="V8" t="s">
         <v>371</v>
-      </c>
-      <c r="V8" t="s">
-        <v>372</v>
       </c>
       <c r="W8" t="s">
         <v>252</v>
@@ -70640,10 +70634,10 @@
         <v>18</v>
       </c>
       <c r="U9" t="s">
+        <v>370</v>
+      </c>
+      <c r="V9" t="s">
         <v>371</v>
-      </c>
-      <c r="V9" t="s">
-        <v>372</v>
       </c>
       <c r="W9" t="s">
         <v>252</v>
@@ -70762,10 +70756,10 @@
         <v>18</v>
       </c>
       <c r="U10" t="s">
+        <v>370</v>
+      </c>
+      <c r="V10" t="s">
         <v>371</v>
-      </c>
-      <c r="V10" t="s">
-        <v>372</v>
       </c>
       <c r="W10" t="s">
         <v>252</v>
@@ -70884,10 +70878,10 @@
         <v>18</v>
       </c>
       <c r="U11" t="s">
+        <v>370</v>
+      </c>
+      <c r="V11" t="s">
         <v>371</v>
-      </c>
-      <c r="V11" t="s">
-        <v>372</v>
       </c>
       <c r="W11" t="s">
         <v>252</v>
@@ -71006,10 +71000,10 @@
         <v>18</v>
       </c>
       <c r="U12" t="s">
+        <v>370</v>
+      </c>
+      <c r="V12" t="s">
         <v>371</v>
-      </c>
-      <c r="V12" t="s">
-        <v>372</v>
       </c>
       <c r="W12" t="s">
         <v>252</v>
@@ -71128,10 +71122,10 @@
         <v>18</v>
       </c>
       <c r="U13" t="s">
+        <v>370</v>
+      </c>
+      <c r="V13" t="s">
         <v>371</v>
-      </c>
-      <c r="V13" t="s">
-        <v>372</v>
       </c>
       <c r="W13" t="s">
         <v>252</v>
@@ -71250,10 +71244,10 @@
         <v>18</v>
       </c>
       <c r="U14" t="s">
+        <v>370</v>
+      </c>
+      <c r="V14" t="s">
         <v>371</v>
-      </c>
-      <c r="V14" t="s">
-        <v>372</v>
       </c>
       <c r="W14" t="s">
         <v>252</v>
@@ -71372,10 +71366,10 @@
         <v>18</v>
       </c>
       <c r="U15" t="s">
+        <v>370</v>
+      </c>
+      <c r="V15" t="s">
         <v>371</v>
-      </c>
-      <c r="V15" t="s">
-        <v>372</v>
       </c>
       <c r="W15" t="s">
         <v>252</v>
@@ -71494,10 +71488,10 @@
         <v>18</v>
       </c>
       <c r="U16" t="s">
+        <v>370</v>
+      </c>
+      <c r="V16" t="s">
         <v>371</v>
-      </c>
-      <c r="V16" t="s">
-        <v>372</v>
       </c>
       <c r="W16" t="s">
         <v>252</v>
@@ -71616,10 +71610,10 @@
         <v>18</v>
       </c>
       <c r="U17" t="s">
+        <v>370</v>
+      </c>
+      <c r="V17" t="s">
         <v>371</v>
-      </c>
-      <c r="V17" t="s">
-        <v>372</v>
       </c>
       <c r="W17" t="s">
         <v>252</v>
@@ -71738,10 +71732,10 @@
         <v>18</v>
       </c>
       <c r="U18" t="s">
+        <v>370</v>
+      </c>
+      <c r="V18" t="s">
         <v>371</v>
-      </c>
-      <c r="V18" t="s">
-        <v>372</v>
       </c>
       <c r="W18" t="s">
         <v>252</v>
@@ -71860,10 +71854,10 @@
         <v>18</v>
       </c>
       <c r="U19" t="s">
+        <v>370</v>
+      </c>
+      <c r="V19" t="s">
         <v>371</v>
-      </c>
-      <c r="V19" t="s">
-        <v>372</v>
       </c>
       <c r="W19" t="s">
         <v>252</v>
@@ -71982,10 +71976,10 @@
         <v>18</v>
       </c>
       <c r="U20" t="s">
+        <v>370</v>
+      </c>
+      <c r="V20" t="s">
         <v>371</v>
-      </c>
-      <c r="V20" t="s">
-        <v>372</v>
       </c>
       <c r="W20" t="s">
         <v>252</v>
@@ -72104,10 +72098,10 @@
         <v>18</v>
       </c>
       <c r="U21" t="s">
+        <v>370</v>
+      </c>
+      <c r="V21" t="s">
         <v>371</v>
-      </c>
-      <c r="V21" t="s">
-        <v>372</v>
       </c>
       <c r="W21" t="s">
         <v>252</v>
@@ -72226,10 +72220,10 @@
         <v>18</v>
       </c>
       <c r="U22" t="s">
+        <v>370</v>
+      </c>
+      <c r="V22" t="s">
         <v>371</v>
-      </c>
-      <c r="V22" t="s">
-        <v>372</v>
       </c>
       <c r="W22" t="s">
         <v>252</v>
@@ -72348,10 +72342,10 @@
         <v>18</v>
       </c>
       <c r="U23" t="s">
+        <v>370</v>
+      </c>
+      <c r="V23" t="s">
         <v>371</v>
-      </c>
-      <c r="V23" t="s">
-        <v>372</v>
       </c>
       <c r="W23" t="s">
         <v>252</v>
@@ -72470,10 +72464,10 @@
         <v>18</v>
       </c>
       <c r="U24" t="s">
+        <v>370</v>
+      </c>
+      <c r="V24" t="s">
         <v>371</v>
-      </c>
-      <c r="V24" t="s">
-        <v>372</v>
       </c>
       <c r="W24" t="s">
         <v>252</v>
@@ -72592,10 +72586,10 @@
         <v>18</v>
       </c>
       <c r="U25" t="s">
+        <v>370</v>
+      </c>
+      <c r="V25" t="s">
         <v>371</v>
-      </c>
-      <c r="V25" t="s">
-        <v>372</v>
       </c>
       <c r="W25" t="s">
         <v>252</v>
@@ -72714,10 +72708,10 @@
         <v>18</v>
       </c>
       <c r="U26" t="s">
+        <v>370</v>
+      </c>
+      <c r="V26" t="s">
         <v>371</v>
-      </c>
-      <c r="V26" t="s">
-        <v>372</v>
       </c>
       <c r="W26" t="s">
         <v>252</v>
@@ -72836,10 +72830,10 @@
         <v>18</v>
       </c>
       <c r="U27" t="s">
+        <v>370</v>
+      </c>
+      <c r="V27" t="s">
         <v>371</v>
-      </c>
-      <c r="V27" t="s">
-        <v>372</v>
       </c>
       <c r="W27" t="s">
         <v>252</v>
@@ -72958,10 +72952,10 @@
         <v>18</v>
       </c>
       <c r="U28" t="s">
+        <v>370</v>
+      </c>
+      <c r="V28" t="s">
         <v>371</v>
-      </c>
-      <c r="V28" t="s">
-        <v>372</v>
       </c>
       <c r="W28" t="s">
         <v>252</v>
@@ -73080,10 +73074,10 @@
         <v>18</v>
       </c>
       <c r="U29" t="s">
+        <v>370</v>
+      </c>
+      <c r="V29" t="s">
         <v>371</v>
-      </c>
-      <c r="V29" t="s">
-        <v>372</v>
       </c>
       <c r="W29" t="s">
         <v>252</v>
@@ -73202,10 +73196,10 @@
         <v>18</v>
       </c>
       <c r="U30" t="s">
+        <v>370</v>
+      </c>
+      <c r="V30" t="s">
         <v>371</v>
-      </c>
-      <c r="V30" t="s">
-        <v>372</v>
       </c>
       <c r="W30" t="s">
         <v>252</v>
@@ -73324,10 +73318,10 @@
         <v>18</v>
       </c>
       <c r="U31" t="s">
+        <v>370</v>
+      </c>
+      <c r="V31" t="s">
         <v>371</v>
-      </c>
-      <c r="V31" t="s">
-        <v>372</v>
       </c>
       <c r="W31" t="s">
         <v>252</v>
@@ -73446,10 +73440,10 @@
         <v>18</v>
       </c>
       <c r="U32" t="s">
+        <v>370</v>
+      </c>
+      <c r="V32" t="s">
         <v>371</v>
-      </c>
-      <c r="V32" t="s">
-        <v>372</v>
       </c>
       <c r="W32" t="s">
         <v>252</v>
@@ -73568,10 +73562,10 @@
         <v>18</v>
       </c>
       <c r="U33" t="s">
+        <v>370</v>
+      </c>
+      <c r="V33" t="s">
         <v>371</v>
-      </c>
-      <c r="V33" t="s">
-        <v>372</v>
       </c>
       <c r="W33" t="s">
         <v>252</v>
@@ -73690,10 +73684,10 @@
         <v>18</v>
       </c>
       <c r="U34" t="s">
+        <v>370</v>
+      </c>
+      <c r="V34" t="s">
         <v>371</v>
-      </c>
-      <c r="V34" t="s">
-        <v>372</v>
       </c>
       <c r="W34" t="s">
         <v>252</v>
@@ -73812,10 +73806,10 @@
         <v>18</v>
       </c>
       <c r="U35" t="s">
+        <v>370</v>
+      </c>
+      <c r="V35" t="s">
         <v>371</v>
-      </c>
-      <c r="V35" t="s">
-        <v>372</v>
       </c>
       <c r="W35" t="s">
         <v>252</v>
@@ -73895,13 +73889,13 @@
         <v>0.03402</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0103</v>
+        <v>0.0075</v>
       </c>
       <c r="I36" t="n">
         <v>0.2608</v>
       </c>
       <c r="J36" t="n">
-        <v>0.07535400000000003</v>
+        <v>0.07262000000000002</v>
       </c>
       <c r="K36" t="s">
         <v>251</v>
@@ -73919,25 +73913,25 @@
         <v>55</v>
       </c>
       <c r="P36" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0146</v>
+        <v>0.015</v>
       </c>
       <c r="R36" t="n">
         <v>62892.0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.48</v>
+        <v>0.618899</v>
       </c>
       <c r="T36" t="s">
         <v>18</v>
       </c>
       <c r="U36" t="s">
+        <v>370</v>
+      </c>
+      <c r="V36" t="s">
         <v>371</v>
-      </c>
-      <c r="V36" t="s">
-        <v>372</v>
       </c>
       <c r="W36" t="s">
         <v>252</v>
@@ -73952,7 +73946,7 @@
         <v>189</v>
       </c>
       <c r="AA36" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AB36" t="s">
         <v>247</v>
@@ -73961,10 +73955,10 @@
         <v>250</v>
       </c>
       <c r="AD36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AE36" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AF36" t="n">
         <v>0.094391</v>
@@ -74056,10 +74050,10 @@
         <v>18</v>
       </c>
       <c r="U37" t="s">
+        <v>370</v>
+      </c>
+      <c r="V37" t="s">
         <v>371</v>
-      </c>
-      <c r="V37" t="s">
-        <v>372</v>
       </c>
       <c r="W37" t="s">
         <v>252</v>
@@ -74178,10 +74172,10 @@
         <v>18</v>
       </c>
       <c r="U38" t="s">
+        <v>370</v>
+      </c>
+      <c r="V38" t="s">
         <v>371</v>
-      </c>
-      <c r="V38" t="s">
-        <v>372</v>
       </c>
       <c r="W38" t="s">
         <v>252</v>
@@ -74300,10 +74294,10 @@
         <v>18</v>
       </c>
       <c r="U39" t="s">
+        <v>370</v>
+      </c>
+      <c r="V39" t="s">
         <v>371</v>
-      </c>
-      <c r="V39" t="s">
-        <v>372</v>
       </c>
       <c r="W39" t="s">
         <v>252</v>
@@ -74422,10 +74416,10 @@
         <v>18</v>
       </c>
       <c r="U40" t="s">
+        <v>370</v>
+      </c>
+      <c r="V40" t="s">
         <v>371</v>
-      </c>
-      <c r="V40" t="s">
-        <v>372</v>
       </c>
       <c r="W40" t="s">
         <v>252</v>
@@ -74544,10 +74538,10 @@
         <v>18</v>
       </c>
       <c r="U41" t="s">
+        <v>370</v>
+      </c>
+      <c r="V41" t="s">
         <v>371</v>
-      </c>
-      <c r="V41" t="s">
-        <v>372</v>
       </c>
       <c r="W41" t="s">
         <v>252</v>
@@ -74666,10 +74660,10 @@
         <v>18</v>
       </c>
       <c r="U42" t="s">
+        <v>370</v>
+      </c>
+      <c r="V42" t="s">
         <v>371</v>
-      </c>
-      <c r="V42" t="s">
-        <v>372</v>
       </c>
       <c r="W42" t="s">
         <v>252</v>
@@ -74788,10 +74782,10 @@
         <v>18</v>
       </c>
       <c r="U43" t="s">
+        <v>370</v>
+      </c>
+      <c r="V43" t="s">
         <v>371</v>
-      </c>
-      <c r="V43" t="s">
-        <v>372</v>
       </c>
       <c r="W43" t="s">
         <v>252</v>
@@ -74910,10 +74904,10 @@
         <v>18</v>
       </c>
       <c r="U44" t="s">
+        <v>370</v>
+      </c>
+      <c r="V44" t="s">
         <v>371</v>
-      </c>
-      <c r="V44" t="s">
-        <v>372</v>
       </c>
       <c r="W44" t="s">
         <v>252</v>
@@ -75032,10 +75026,10 @@
         <v>18</v>
       </c>
       <c r="U45" t="s">
+        <v>370</v>
+      </c>
+      <c r="V45" t="s">
         <v>371</v>
-      </c>
-      <c r="V45" t="s">
-        <v>372</v>
       </c>
       <c r="W45" t="s">
         <v>252</v>
@@ -75154,10 +75148,10 @@
         <v>18</v>
       </c>
       <c r="U46" t="s">
+        <v>370</v>
+      </c>
+      <c r="V46" t="s">
         <v>371</v>
-      </c>
-      <c r="V46" t="s">
-        <v>372</v>
       </c>
       <c r="W46" t="s">
         <v>252</v>
@@ -75276,10 +75270,10 @@
         <v>18</v>
       </c>
       <c r="U47" t="s">
+        <v>370</v>
+      </c>
+      <c r="V47" t="s">
         <v>371</v>
-      </c>
-      <c r="V47" t="s">
-        <v>372</v>
       </c>
       <c r="W47" t="s">
         <v>252</v>
@@ -75398,10 +75392,10 @@
         <v>18</v>
       </c>
       <c r="U48" t="s">
+        <v>370</v>
+      </c>
+      <c r="V48" t="s">
         <v>371</v>
-      </c>
-      <c r="V48" t="s">
-        <v>372</v>
       </c>
       <c r="W48" t="s">
         <v>252</v>
@@ -75520,10 +75514,10 @@
         <v>18</v>
       </c>
       <c r="U49" t="s">
+        <v>370</v>
+      </c>
+      <c r="V49" t="s">
         <v>371</v>
-      </c>
-      <c r="V49" t="s">
-        <v>372</v>
       </c>
       <c r="W49" t="s">
         <v>252</v>
@@ -75642,10 +75636,10 @@
         <v>18</v>
       </c>
       <c r="U50" t="s">
+        <v>370</v>
+      </c>
+      <c r="V50" t="s">
         <v>371</v>
-      </c>
-      <c r="V50" t="s">
-        <v>372</v>
       </c>
       <c r="W50" t="s">
         <v>252</v>
@@ -75764,10 +75758,10 @@
         <v>18</v>
       </c>
       <c r="U51" t="s">
+        <v>370</v>
+      </c>
+      <c r="V51" t="s">
         <v>371</v>
-      </c>
-      <c r="V51" t="s">
-        <v>372</v>
       </c>
       <c r="W51" t="s">
         <v>252</v>
@@ -75886,10 +75880,10 @@
         <v>18</v>
       </c>
       <c r="U52" t="s">
+        <v>370</v>
+      </c>
+      <c r="V52" t="s">
         <v>371</v>
-      </c>
-      <c r="V52" t="s">
-        <v>372</v>
       </c>
       <c r="W52" t="s">
         <v>252</v>
@@ -76008,10 +76002,10 @@
         <v>18</v>
       </c>
       <c r="U53" t="s">
+        <v>370</v>
+      </c>
+      <c r="V53" t="s">
         <v>371</v>
-      </c>
-      <c r="V53" t="s">
-        <v>372</v>
       </c>
       <c r="W53" t="s">
         <v>252</v>
@@ -76130,10 +76124,10 @@
         <v>18</v>
       </c>
       <c r="U54" t="s">
+        <v>370</v>
+      </c>
+      <c r="V54" t="s">
         <v>371</v>
-      </c>
-      <c r="V54" t="s">
-        <v>372</v>
       </c>
       <c r="W54" t="s">
         <v>252</v>
@@ -76252,10 +76246,10 @@
         <v>18</v>
       </c>
       <c r="U55" t="s">
+        <v>370</v>
+      </c>
+      <c r="V55" t="s">
         <v>371</v>
-      </c>
-      <c r="V55" t="s">
-        <v>372</v>
       </c>
       <c r="W55" t="s">
         <v>252</v>
@@ -76374,10 +76368,10 @@
         <v>18</v>
       </c>
       <c r="U56" t="s">
+        <v>370</v>
+      </c>
+      <c r="V56" t="s">
         <v>371</v>
-      </c>
-      <c r="V56" t="s">
-        <v>372</v>
       </c>
       <c r="W56" t="s">
         <v>252</v>
@@ -76496,10 +76490,10 @@
         <v>18</v>
       </c>
       <c r="U57" t="s">
+        <v>370</v>
+      </c>
+      <c r="V57" t="s">
         <v>371</v>
-      </c>
-      <c r="V57" t="s">
-        <v>372</v>
       </c>
       <c r="W57" t="s">
         <v>252</v>
@@ -76618,10 +76612,10 @@
         <v>18</v>
       </c>
       <c r="U58" t="s">
+        <v>370</v>
+      </c>
+      <c r="V58" t="s">
         <v>371</v>
-      </c>
-      <c r="V58" t="s">
-        <v>372</v>
       </c>
       <c r="W58" t="s">
         <v>252</v>
@@ -76740,10 +76734,10 @@
         <v>18</v>
       </c>
       <c r="U59" t="s">
+        <v>370</v>
+      </c>
+      <c r="V59" t="s">
         <v>371</v>
-      </c>
-      <c r="V59" t="s">
-        <v>372</v>
       </c>
       <c r="W59" t="s">
         <v>252</v>
@@ -76862,10 +76856,10 @@
         <v>18</v>
       </c>
       <c r="U60" t="s">
+        <v>370</v>
+      </c>
+      <c r="V60" t="s">
         <v>371</v>
-      </c>
-      <c r="V60" t="s">
-        <v>372</v>
       </c>
       <c r="W60" t="s">
         <v>252</v>
@@ -76984,10 +76978,10 @@
         <v>18</v>
       </c>
       <c r="U61" t="s">
+        <v>370</v>
+      </c>
+      <c r="V61" t="s">
         <v>371</v>
-      </c>
-      <c r="V61" t="s">
-        <v>372</v>
       </c>
       <c r="W61" t="s">
         <v>252</v>
@@ -77106,10 +77100,10 @@
         <v>18</v>
       </c>
       <c r="U62" t="s">
+        <v>370</v>
+      </c>
+      <c r="V62" t="s">
         <v>371</v>
-      </c>
-      <c r="V62" t="s">
-        <v>372</v>
       </c>
       <c r="W62" t="s">
         <v>252</v>
@@ -77228,10 +77222,10 @@
         <v>18</v>
       </c>
       <c r="U63" t="s">
+        <v>370</v>
+      </c>
+      <c r="V63" t="s">
         <v>371</v>
-      </c>
-      <c r="V63" t="s">
-        <v>372</v>
       </c>
       <c r="W63" t="s">
         <v>252</v>
@@ -77350,10 +77344,10 @@
         <v>18</v>
       </c>
       <c r="U64" t="s">
+        <v>370</v>
+      </c>
+      <c r="V64" t="s">
         <v>371</v>
-      </c>
-      <c r="V64" t="s">
-        <v>372</v>
       </c>
       <c r="W64" t="s">
         <v>252</v>
@@ -77472,10 +77466,10 @@
         <v>18</v>
       </c>
       <c r="U65" t="s">
+        <v>370</v>
+      </c>
+      <c r="V65" t="s">
         <v>371</v>
-      </c>
-      <c r="V65" t="s">
-        <v>372</v>
       </c>
       <c r="W65" t="s">
         <v>252</v>
@@ -77594,10 +77588,10 @@
         <v>18</v>
       </c>
       <c r="U66" t="s">
+        <v>370</v>
+      </c>
+      <c r="V66" t="s">
         <v>371</v>
-      </c>
-      <c r="V66" t="s">
-        <v>372</v>
       </c>
       <c r="W66" t="s">
         <v>252</v>
@@ -77716,10 +77710,10 @@
         <v>18</v>
       </c>
       <c r="U67" t="s">
+        <v>370</v>
+      </c>
+      <c r="V67" t="s">
         <v>371</v>
-      </c>
-      <c r="V67" t="s">
-        <v>372</v>
       </c>
       <c r="W67" t="s">
         <v>252</v>
@@ -77838,10 +77832,10 @@
         <v>18</v>
       </c>
       <c r="U68" t="s">
+        <v>370</v>
+      </c>
+      <c r="V68" t="s">
         <v>371</v>
-      </c>
-      <c r="V68" t="s">
-        <v>372</v>
       </c>
       <c r="W68" t="s">
         <v>252</v>
@@ -77960,10 +77954,10 @@
         <v>18</v>
       </c>
       <c r="U69" t="s">
+        <v>370</v>
+      </c>
+      <c r="V69" t="s">
         <v>371</v>
-      </c>
-      <c r="V69" t="s">
-        <v>372</v>
       </c>
       <c r="W69" t="s">
         <v>252</v>
@@ -78043,13 +78037,13 @@
         <v>0.028178</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0095</v>
+        <v>0.0094</v>
       </c>
       <c r="I70" t="n">
         <v>0.669</v>
       </c>
       <c r="J70" t="n">
-        <v>0.575772</v>
+        <v>0.574193</v>
       </c>
       <c r="K70" t="s">
         <v>251</v>
@@ -78067,25 +78061,25 @@
         <v>55</v>
       </c>
       <c r="P70" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.0084</v>
+        <v>0.0082</v>
       </c>
       <c r="R70" t="n">
         <v>62892.0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.2589</v>
+        <v>0.2549</v>
       </c>
       <c r="T70" t="s">
         <v>18</v>
       </c>
       <c r="U70" t="s">
+        <v>370</v>
+      </c>
+      <c r="V70" t="s">
         <v>371</v>
-      </c>
-      <c r="V70" t="s">
-        <v>372</v>
       </c>
       <c r="W70" t="s">
         <v>252</v>
@@ -78100,7 +78094,7 @@
         <v>230</v>
       </c>
       <c r="AA70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AB70" t="s">
         <v>250</v>
@@ -78109,10 +78103,10 @@
         <v>249</v>
       </c>
       <c r="AD70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE70" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF70" t="n">
         <v>0.012771</v>
@@ -78204,10 +78198,10 @@
         <v>18</v>
       </c>
       <c r="U71" t="s">
+        <v>370</v>
+      </c>
+      <c r="V71" t="s">
         <v>371</v>
-      </c>
-      <c r="V71" t="s">
-        <v>372</v>
       </c>
       <c r="W71" t="s">
         <v>252</v>
@@ -78326,10 +78320,10 @@
         <v>18</v>
       </c>
       <c r="U72" t="s">
+        <v>370</v>
+      </c>
+      <c r="V72" t="s">
         <v>371</v>
-      </c>
-      <c r="V72" t="s">
-        <v>372</v>
       </c>
       <c r="W72" t="s">
         <v>252</v>
@@ -78448,10 +78442,10 @@
         <v>18</v>
       </c>
       <c r="U73" t="s">
+        <v>370</v>
+      </c>
+      <c r="V73" t="s">
         <v>371</v>
-      </c>
-      <c r="V73" t="s">
-        <v>372</v>
       </c>
       <c r="W73" t="s">
         <v>252</v>
@@ -78570,10 +78564,10 @@
         <v>18</v>
       </c>
       <c r="U74" t="s">
+        <v>370</v>
+      </c>
+      <c r="V74" t="s">
         <v>371</v>
-      </c>
-      <c r="V74" t="s">
-        <v>372</v>
       </c>
       <c r="W74" t="s">
         <v>252</v>
@@ -78692,10 +78686,10 @@
         <v>18</v>
       </c>
       <c r="U75" t="s">
+        <v>370</v>
+      </c>
+      <c r="V75" t="s">
         <v>371</v>
-      </c>
-      <c r="V75" t="s">
-        <v>372</v>
       </c>
       <c r="W75" t="s">
         <v>252</v>
@@ -78814,10 +78808,10 @@
         <v>18</v>
       </c>
       <c r="U76" t="s">
+        <v>370</v>
+      </c>
+      <c r="V76" t="s">
         <v>371</v>
-      </c>
-      <c r="V76" t="s">
-        <v>372</v>
       </c>
       <c r="W76" t="s">
         <v>252</v>
@@ -78936,10 +78930,10 @@
         <v>18</v>
       </c>
       <c r="U77" t="s">
+        <v>370</v>
+      </c>
+      <c r="V77" t="s">
         <v>371</v>
-      </c>
-      <c r="V77" t="s">
-        <v>372</v>
       </c>
       <c r="W77" t="s">
         <v>252</v>
@@ -79058,10 +79052,10 @@
         <v>18</v>
       </c>
       <c r="U78" t="s">
+        <v>370</v>
+      </c>
+      <c r="V78" t="s">
         <v>371</v>
-      </c>
-      <c r="V78" t="s">
-        <v>372</v>
       </c>
       <c r="W78" t="s">
         <v>252</v>
@@ -79180,10 +79174,10 @@
         <v>18</v>
       </c>
       <c r="U79" t="s">
+        <v>370</v>
+      </c>
+      <c r="V79" t="s">
         <v>371</v>
-      </c>
-      <c r="V79" t="s">
-        <v>372</v>
       </c>
       <c r="W79" t="s">
         <v>252</v>
@@ -79302,10 +79296,10 @@
         <v>18</v>
       </c>
       <c r="U80" t="s">
+        <v>370</v>
+      </c>
+      <c r="V80" t="s">
         <v>371</v>
-      </c>
-      <c r="V80" t="s">
-        <v>372</v>
       </c>
       <c r="W80" t="s">
         <v>252</v>
@@ -79424,10 +79418,10 @@
         <v>18</v>
       </c>
       <c r="U81" t="s">
+        <v>370</v>
+      </c>
+      <c r="V81" t="s">
         <v>371</v>
-      </c>
-      <c r="V81" t="s">
-        <v>372</v>
       </c>
       <c r="W81" t="s">
         <v>252</v>
@@ -79546,10 +79540,10 @@
         <v>18</v>
       </c>
       <c r="U82" t="s">
+        <v>370</v>
+      </c>
+      <c r="V82" t="s">
         <v>371</v>
-      </c>
-      <c r="V82" t="s">
-        <v>372</v>
       </c>
       <c r="W82" t="s">
         <v>252</v>
@@ -79668,10 +79662,10 @@
         <v>18</v>
       </c>
       <c r="U83" t="s">
+        <v>370</v>
+      </c>
+      <c r="V83" t="s">
         <v>371</v>
-      </c>
-      <c r="V83" t="s">
-        <v>372</v>
       </c>
       <c r="W83" t="s">
         <v>252</v>
@@ -79790,10 +79784,10 @@
         <v>18</v>
       </c>
       <c r="U84" t="s">
+        <v>370</v>
+      </c>
+      <c r="V84" t="s">
         <v>371</v>
-      </c>
-      <c r="V84" t="s">
-        <v>372</v>
       </c>
       <c r="W84" t="s">
         <v>252</v>
@@ -79873,13 +79867,13 @@
         <v>0.016758</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01</v>
+        <v>0.0101</v>
       </c>
       <c r="I85" t="n">
         <v>0.0594</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0759323</v>
+        <v>0.0762936</v>
       </c>
       <c r="K85" t="s">
         <v>251</v>
@@ -79897,7 +79891,7 @@
         <v>55</v>
       </c>
       <c r="P85" t="s">
-        <v>370</v>
+        <v>319</v>
       </c>
       <c r="Q85" t="n">
         <v>0.0147</v>
@@ -79906,16 +79900,16 @@
         <v>62892.0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.4968</v>
+        <v>0.4903</v>
       </c>
       <c r="T85" t="s">
         <v>18</v>
       </c>
       <c r="U85" t="s">
+        <v>370</v>
+      </c>
+      <c r="V85" t="s">
         <v>371</v>
-      </c>
-      <c r="V85" t="s">
-        <v>372</v>
       </c>
       <c r="W85" t="s">
         <v>252</v>
@@ -79930,7 +79924,7 @@
         <v>245</v>
       </c>
       <c r="AA85" t="s">
-        <v>373</v>
+        <v>210</v>
       </c>
       <c r="AB85" t="s">
         <v>249</v>
@@ -80034,10 +80028,10 @@
         <v>18</v>
       </c>
       <c r="U86" t="s">
+        <v>370</v>
+      </c>
+      <c r="V86" t="s">
         <v>371</v>
-      </c>
-      <c r="V86" t="s">
-        <v>372</v>
       </c>
       <c r="W86" t="s">
         <v>252</v>

--- a/Colocalization/data.xlsx
+++ b/Colocalization/data.xlsx
@@ -1037,10 +1037,10 @@
     <t>41828496</t>
   </si>
   <si>
-    <t>41829296</t>
+    <t>41829779</t>
   </si>
   <si>
-    <t>41829779</t>
+    <t>41829296</t>
   </si>
   <si>
     <t>41835215</t>
@@ -6936,13 +6936,13 @@
         <v>0.03402</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0244466</v>
+        <v>-0.0260167</v>
       </c>
       <c r="I48" t="n">
         <v>0.2608</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07582900000000004</v>
+        <v>0.07303700000000002</v>
       </c>
       <c r="K48" t="s">
         <v>251</v>
@@ -6960,16 +6960,16 @@
         <v>55</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.00349056</v>
+        <v>0.00355141</v>
       </c>
       <c r="R48" t="n">
         <v>426824.0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.0E-9</v>
+        <v>6.90001E-10</v>
       </c>
       <c r="T48" t="s">
         <v>18</v>
@@ -6993,7 +6993,7 @@
         <v>189</v>
       </c>
       <c r="AA48" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AB48" t="s">
         <v>247</v>
@@ -7002,10 +7002,10 @@
         <v>250</v>
       </c>
       <c r="AD48" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AE48" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AF48" t="n">
         <v>0.094391</v>
@@ -11938,13 +11938,13 @@
         <v>0.028178</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.0180004</v>
+        <v>-0.0181372</v>
       </c>
       <c r="I89" t="n">
         <v>0.669</v>
       </c>
       <c r="J89" t="n">
-        <v>0.5749960000000001</v>
+        <v>0.5738099999999999</v>
       </c>
       <c r="K89" t="s">
         <v>251</v>
@@ -11965,13 +11965,13 @@
         <v>339</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.00187438</v>
+        <v>0.00187369</v>
       </c>
       <c r="R89" t="n">
         <v>426824.0</v>
       </c>
       <c r="S89" t="n">
-        <v>1.20005E-18</v>
+        <v>1.0E-18</v>
       </c>
       <c r="T89" t="s">
         <v>18</v>
@@ -11995,7 +11995,7 @@
         <v>230</v>
       </c>
       <c r="AA89" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AB89" t="s">
         <v>250</v>
@@ -12004,10 +12004,10 @@
         <v>249</v>
       </c>
       <c r="AD89" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE89" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF89" t="n">
         <v>0.012771</v>
@@ -12084,7 +12084,7 @@
         <v>55</v>
       </c>
       <c r="P90" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q90" t="n">
         <v>0.00187438</v>
@@ -12206,7 +12206,7 @@
         <v>55</v>
       </c>
       <c r="P91" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q91" t="n">
         <v>0.00187369</v>
@@ -33856,7 +33856,7 @@
         <v>55</v>
       </c>
       <c r="P86" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q86" t="n">
         <v>0.0057</v>
@@ -33978,7 +33978,7 @@
         <v>55</v>
       </c>
       <c r="P87" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q87" t="n">
         <v>0.0057</v>
@@ -34100,7 +34100,7 @@
         <v>55</v>
       </c>
       <c r="P88" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q88" t="n">
         <v>0.0057</v>
@@ -46186,7 +46186,7 @@
         <v>55</v>
       </c>
       <c r="P85" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q85" t="n">
         <v>0.007509</v>
@@ -46308,7 +46308,7 @@
         <v>55</v>
       </c>
       <c r="P86" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q86" t="n">
         <v>0.007515</v>
@@ -62535,13 +62535,13 @@
         <v>0.03402</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.00103282</v>
+        <v>-4.70585E-4</v>
       </c>
       <c r="I49" t="n">
         <v>0.2608</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07655500000000004</v>
+        <v>0.07318599999999997</v>
       </c>
       <c r="K49" t="s">
         <v>251</v>
@@ -62559,16 +62559,16 @@
         <v>55</v>
       </c>
       <c r="P49" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.00168897</v>
+        <v>0.00172462</v>
       </c>
       <c r="R49" t="n">
         <v>462933.0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.54</v>
+        <v>0.780001</v>
       </c>
       <c r="T49" t="s">
         <v>18</v>
@@ -62592,7 +62592,7 @@
         <v>189</v>
       </c>
       <c r="AA49" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AB49" t="s">
         <v>247</v>
@@ -62601,10 +62601,10 @@
         <v>250</v>
       </c>
       <c r="AD49" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AE49" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AF49" t="n">
         <v>0.094391</v>
@@ -67537,13 +67537,13 @@
         <v>0.028178</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.3434E-4</v>
+        <v>-8.79383E-5</v>
       </c>
       <c r="I90" t="n">
         <v>0.669</v>
       </c>
       <c r="J90" t="n">
-        <v>0.575968</v>
+        <v>0.5747340000000001</v>
       </c>
       <c r="K90" t="s">
         <v>251</v>
@@ -67564,13 +67564,13 @@
         <v>339</v>
       </c>
       <c r="Q90" t="n">
-        <v>9.10619E-4</v>
+        <v>9.10266E-4</v>
       </c>
       <c r="R90" t="n">
         <v>462933.0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="T90" t="s">
         <v>18</v>
@@ -67594,7 +67594,7 @@
         <v>230</v>
       </c>
       <c r="AA90" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AB90" t="s">
         <v>250</v>
@@ -67603,10 +67603,10 @@
         <v>249</v>
       </c>
       <c r="AD90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE90" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF90" t="n">
         <v>0.012771</v>
@@ -67683,7 +67683,7 @@
         <v>55</v>
       </c>
       <c r="P91" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q91" t="n">
         <v>9.10619E-4</v>
@@ -67805,7 +67805,7 @@
         <v>55</v>
       </c>
       <c r="P92" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q92" t="n">
         <v>9.10266E-4</v>
@@ -78061,7 +78061,7 @@
         <v>55</v>
       </c>
       <c r="P70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q70" t="n">
         <v>0.0082</v>
@@ -78183,7 +78183,7 @@
         <v>55</v>
       </c>
       <c r="P71" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q71" t="n">
         <v>0.0084</v>
@@ -78305,7 +78305,7 @@
         <v>55</v>
       </c>
       <c r="P72" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q72" t="n">
         <v>0.0082</v>
